--- a/output/pdf_financials_xlsx/SCLT.xlsx
+++ b/output/pdf_financials_xlsx/SCLT.xlsx
@@ -6106,25 +6106,25 @@
         <v>8.696561000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.722509000000001</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>9.058164</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.346401</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.539183</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>9.514113</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>9.453225</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>9.148764999999999</v>
       </c>
     </row>
     <row r="93">
@@ -9726,7 +9726,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10310,7 +10314,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11690,7 +11698,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SCLT.xlsx
+++ b/output/pdf_financials_xlsx/SCLT.xlsx
@@ -989,43 +989,43 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.838686</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.495658</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.166336</v>
+        <v>0.339323</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.206785</v>
+        <v>0.387687</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.187615</v>
+        <v>0.324066</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.482516</v>
+        <v>1.38972</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.309165</v>
+        <v>0.55138</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.259518</v>
+        <v>0.857631</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.3854</v>
+        <v>1.2996</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.418355</v>
+        <v>1.242166</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.56919</v>
+        <v>1.461529</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.344762</v>
+        <v>1.291004</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.246574</v>
+        <v>0.608219</v>
       </c>
     </row>
     <row r="11">
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.166336</v>
+        <v>-0.339323</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.206785</v>
+        <v>-0.387687</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.187615</v>
+        <v>-0.324066</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.482516</v>
+        <v>-1.38972</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.309165</v>
+        <v>-0.55138</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-0.857631</v>
@@ -2608,55 +2608,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.427116</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.252918</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.226964</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.731919</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.040939</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.117742</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.142922</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.041321</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.08164399999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.417941</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.024827</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.883717</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.196294</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.403267</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.265091</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.182928</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.078525</v>
       </c>
     </row>
     <row r="35">
@@ -2724,55 +2724,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.427116</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.252918</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.226964</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.731919</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.040939</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.117742</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.025294</v>
+        <v>0.168216</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.360282</v>
+        <v>0.401603</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1395</v>
+        <v>0.221144</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.023896</v>
+        <v>0.441837</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.01062</v>
+        <v>0.035447</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.274118</v>
+        <v>1.157835</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.164471</v>
+        <v>1.360765</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.065788</v>
+        <v>1.469055</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.047723</v>
+        <v>1.312814</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.014206</v>
+        <v>0.197134</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.035266</v>
+        <v>0.113791</v>
       </c>
     </row>
     <row r="37">
@@ -3423,52 +3423,52 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.256269</v>
+        <v>0.003351</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.270655</v>
+        <v>0.043691</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.786502</v>
+        <v>0.054583</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.046402</v>
+        <v>0.005463</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.118777</v>
+        <v>0.001035</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.143372</v>
+        <v>0.00045</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.041321</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.084235</v>
+        <v>0.002591</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.457557</v>
+        <v>0.039616</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.038378</v>
+        <v>0.013551</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.9188269999999999</v>
+        <v>0.03511</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.243755</v>
+        <v>0.047461</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.473769</v>
+        <v>0.070502</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.359244</v>
+        <v>0.094153</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.272807</v>
+        <v>0.089879</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.104076</v>
+        <v>0.025551</v>
       </c>
     </row>
     <row r="49">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -34348,7 +34348,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -37701,7 +37701,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">

--- a/output/pdf_financials_xlsx/SCLT.xlsx
+++ b/output/pdf_financials_xlsx/SCLT.xlsx
@@ -7391,16 +7391,16 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.159462</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.170717</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.022928</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.053685</v>
       </c>
     </row>
     <row r="116">
@@ -18578,7 +18578,11 @@
           <t>Proceeds from sale of marketable securities-net</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -21891,7 +21895,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
